--- a/docs/resources/QUT-Organization.xlsx
+++ b/docs/resources/QUT-Organization.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A10A9A5-1663-448F-9997-AD6A8012EA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="学生社团" sheetId="1" r:id="rId1"/>

--- a/docs/resources/QUT-Organization.xlsx
+++ b/docs/resources/QUT-Organization.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\QUTWiKi\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A10A9A5-1663-448F-9997-AD6A8012EA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A41DAA8-D032-4EB5-B905-C72CDD899F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="学生社团" sheetId="1" r:id="rId1"/>
     <sheet name="实验室" sheetId="2" r:id="rId2"/>
+    <sheet name="兴趣群" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -4934,4 +4935,14 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{737FB3C0-6823-403A-8DD9-4EAA89A79392}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>